--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.49657984264046</v>
+        <v>6.093194224429075</v>
       </c>
       <c r="D2" t="n">
-        <v>37.20555606902908</v>
+        <v>6.045902861217225</v>
       </c>
       <c r="E2" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F2" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.87928525698928</v>
+        <v>10.21788385426076</v>
       </c>
       <c r="D3" t="n">
-        <v>77.38386814896124</v>
+        <v>12.5748785742062</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F3" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.50849867674817</v>
+        <v>6.745131034971577</v>
       </c>
       <c r="D4" t="n">
-        <v>55.70309451826346</v>
+        <v>9.051752859217812</v>
       </c>
       <c r="E4" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F4" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.53080247503521</v>
+        <v>3.498755402193221</v>
       </c>
       <c r="D5" t="n">
-        <v>21.81380408580483</v>
+        <v>3.544743163943285</v>
       </c>
       <c r="E5" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F5" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.65870722235904</v>
+        <v>3.844539923633345</v>
       </c>
       <c r="D6" t="n">
-        <v>33.11654909202042</v>
+        <v>5.381439227453319</v>
       </c>
       <c r="E6" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F6" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.34823538261401</v>
+        <v>3.306588249674777</v>
       </c>
       <c r="D7" t="n">
-        <v>34.52661993696861</v>
+        <v>5.6105757397574</v>
       </c>
       <c r="E7" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F7" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.66032939504611</v>
+        <v>5.794803526694992</v>
       </c>
       <c r="D8" t="n">
-        <v>39.37698582629042</v>
+        <v>6.398760196772193</v>
       </c>
       <c r="E8" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F8" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82374610987349</v>
+        <v>6.633858742854442</v>
       </c>
       <c r="D9" t="n">
-        <v>53.07041992285887</v>
+        <v>8.623943237464568</v>
       </c>
       <c r="E9" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F9" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.0144396912748</v>
+        <v>7.314846449832156</v>
       </c>
       <c r="D10" t="n">
-        <v>45.16232146529807</v>
+        <v>7.338877238110936</v>
       </c>
       <c r="E10" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F10" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.58125279935837</v>
+        <v>7.244453579895736</v>
       </c>
       <c r="D11" t="n">
-        <v>52.32867253932099</v>
+        <v>8.503409287639661</v>
       </c>
       <c r="E11" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F11" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.03538263972175</v>
+        <v>7.480749678954785</v>
       </c>
       <c r="D12" t="n">
-        <v>37.17991653694087</v>
+        <v>6.041736437252892</v>
       </c>
       <c r="E12" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F12" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.35911105660715</v>
+        <v>7.370855546698663</v>
       </c>
       <c r="D13" t="n">
-        <v>49.27677663325971</v>
+        <v>8.007476202904703</v>
       </c>
       <c r="E13" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F13" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.1335629103741</v>
+        <v>8.146703972935793</v>
       </c>
       <c r="D14" t="n">
-        <v>22.5</v>
+        <v>3.65625</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F14" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>62.37991163934254</v>
+        <v>10.13673564139316</v>
       </c>
       <c r="D15" t="n">
-        <v>17.67059704707229</v>
+        <v>2.871472020149247</v>
       </c>
       <c r="E15" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F15" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.22831340992548</v>
+        <v>6.37460092911289</v>
       </c>
       <c r="D16" t="n">
-        <v>7.433034373659253</v>
+        <v>1.207868085719629</v>
       </c>
       <c r="E16" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F16" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.32112010316562</v>
+        <v>8.014682016764413</v>
       </c>
       <c r="D17" t="n">
-        <v>5.813688647876186</v>
+        <v>0.9447244052798803</v>
       </c>
       <c r="E17" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F17" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.17453361799295</v>
+        <v>4.740861712923855</v>
       </c>
       <c r="D18" t="n">
-        <v>75.38206327587612</v>
+        <v>12.24958528232987</v>
       </c>
       <c r="E18" t="n">
-        <v>12.00950992877082</v>
+        <v>1.951545363425258</v>
       </c>
       <c r="F18" t="n">
-        <v>19.96559956450109</v>
+        <v>3.244409929231427</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
